--- a/output/tables/enighur_ingresos_y_gastos_resumen.xlsx
+++ b/output/tables/enighur_ingresos_y_gastos_resumen.xlsx
@@ -12,13 +12,14 @@
     <sheet name="percentiles_ingreso" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="shares_comparison" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="ingreso_agricola" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ahorro" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="notes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t xml:space="preserve">componente</t>
   </si>
@@ -389,6 +390,15 @@
     <t xml:space="preserve">Ingreso monetario total</t>
   </si>
   <si>
+    <t xml:space="preserve">media_ahorro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mediana_ahorro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENIGHUR 2011-2012 (precios 2024-2025)</t>
+  </si>
+  <si>
     <t xml:space="preserve">item</t>
   </si>
   <si>
@@ -429,13 +439,25 @@
   </si>
   <si>
     <t xml:space="preserve">Ingreso no agricola is defined here as ingreso monetario total minus ingreso agricola neto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ahorro_definition_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENIGHUR 2024-2025 savings: monetary savings = ing_mon_cor - gas_mon_cor (monetary current income minus monetary current spending). Weighted mean and median at household level.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ahorro_definition_2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENIGHUR 2011-2012 savings: reconstructed monetary ing_mon_cor (INEC SPSS syntax) minus total purchases from GASTOS_HTOT (all survey instruments: daily diaries + monthly + quarterly + annual). HTOT individual items identified by variable-name length (7 chars divs 1-9, 8 chars divs 10-12) excluding zero-filled SPSS subtotals (vars ending in '00'). HTOT national weighted mean ≈ $788/month nominal (97% of TABULADOS $809). Both deflated to 2024-2025 prices (IPC 1.2631). Negative savings in 2012 reflect that monetary income (~$708/month nominal) was less than total market purchases (~$788/month nominal); the gap was financed by non-monetary income (own agricultural production, imputed housing, etc.) not captured in ing_mon_cor. Weighted mean and median at household level.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="166" formatCode="$#,##0"/>
     <numFmt numFmtId="167" formatCode="$#,##0"/>
     <numFmt numFmtId="168" formatCode="$#,##0"/>
@@ -444,6 +466,7 @@
     <numFmt numFmtId="171" formatCode="0.0%"/>
     <numFmt numFmtId="172" formatCode="$#,##0"/>
     <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="174" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -495,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -506,12 +529,24 @@
     <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:B9" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:B9"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="item"/>
+    <tableColumn id="2" name="detail"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -604,11 +639,13 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:B7" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:B7"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="item"/>
-    <tableColumn id="2" name="detail"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:D7" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D7"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="encuesta"/>
+    <tableColumn id="2" name="zona"/>
+    <tableColumn id="3" name="media_ahorro"/>
+    <tableColumn id="4" name="mediana_ahorro"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3559,64 +3596,108 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="162.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="37.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>72</v>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>205.489620870764</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>68.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>74</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>224.790194168331</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>78.14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>75</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>146.500323454139</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>49.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>72</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>-101.277142104836</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>-117.336166491858</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>74</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>-101.241059661437</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>-133.608297223506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>-101.353742058171</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>-94.7656896865888</v>
       </c>
     </row>
   </sheetData>
@@ -3626,4 +3707,94 @@
     <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="250.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId10"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/output/tables/enighur_ingresos_y_gastos_resumen.xlsx
+++ b/output/tables/enighur_ingresos_y_gastos_resumen.xlsx
@@ -450,7 +450,7 @@
     <t xml:space="preserve">ahorro_definition_2012</t>
   </si>
   <si>
-    <t xml:space="preserve">ENIGHUR 2011-2012 savings: reconstructed monetary ing_mon_cor (INEC SPSS syntax) minus total purchases from GASTOS_HTOT (all survey instruments: daily diaries + monthly + quarterly + annual). HTOT individual items identified by variable-name length (7 chars divs 1-9, 8 chars divs 10-12) excluding zero-filled SPSS subtotals (vars ending in '00'). HTOT national weighted mean ≈ $788/month nominal (97% of TABULADOS $809). Both deflated to 2024-2025 prices (IPC 1.2631). Negative savings in 2012 reflect that monetary income (~$708/month nominal) was less than total market purchases (~$788/month nominal); the gap was financed by non-monetary income (own agricultural production, imputed housing, etc.) not captured in ing_mon_cor. Weighted mean and median at household level.</t>
+    <t xml:space="preserve">ENIGHUR 2011-2012 savings: monetary savings = reconstructed ing_mon_cor minus reconstructed gas_mon_cor, following the official INEC SPSS syntax. Monetary spending is gas_gru_cor + ot_gas_mon, using d1-d12 from GASTOS_HMO plus non-consumption monetary spending from INGRESOS_H. Both deflated to 2024-2025 prices (IPC factor 1.2631). Weighted mean and median at household level.</t>
   </si>
 </sst>
 </file>
@@ -3666,10 +3666,10 @@
         <v>72</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>-101.277142104836</v>
+        <v>720.716464583814</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>-117.336166491858</v>
+        <v>448.555071775226</v>
       </c>
     </row>
     <row r="6">
@@ -3680,10 +3680,10 @@
         <v>74</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>-101.241059661437</v>
+        <v>865.455973258512</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>-133.608297223506</v>
+        <v>558.649824332172</v>
       </c>
     </row>
     <row r="7">
@@ -3694,10 +3694,10 @@
         <v>75</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>-101.353742058171</v>
+        <v>409.79912290714</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>-94.7656896865888</v>
+        <v>286.132683289779</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/enighur_ingresos_y_gastos_resumen.xlsx
+++ b/output/tables/enighur_ingresos_y_gastos_resumen.xlsx
@@ -9,17 +9,25 @@
     <sheet name="medianas" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="gasto_provincia" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ingreso_gasto_total_zona" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="percentiles_ingreso" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="shares_comparison" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ingreso_agricola" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ahorro" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="notes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ingresos y gastos urbano rural" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="componentes urbano rural" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="quintiles ingreso gasto" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="componentes quintiles" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="chart gasto quintiles" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="gasolina quintiles" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="gasolina zona" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="q5 provincias" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="percentiles_ingreso" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="shares_comparison" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ingreso_agricola" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ahorro" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="notes" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t xml:space="preserve">componente</t>
   </si>
@@ -240,6 +248,9 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
+    <t xml:space="preserve">Gasto monetario total del hogar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ingreso monetario total del hogar</t>
   </si>
   <si>
@@ -249,33 +260,153 @@
     <t xml:space="preserve">Rural</t>
   </si>
   <si>
+    <t xml:space="preserve">estadistico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d1_p10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q1_p20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3_p30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q2_p40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mediana_p50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q3_p60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d7_p70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q4_p80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d9_p90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brecha_urbana_menos_rural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alimentos y restaurantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_alimentacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivienda y servicios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_vivienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muebles y hogar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_hogar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vestimenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_vestimenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_transporte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_salud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recreación y educación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_recreacion_educacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat_otros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quintil_ingreso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mediana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percentil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_mean_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_median_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_share_with_spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share_of_gasto_monetario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_mean_spenders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_median_spenders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_households</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share_q5_households</t>
+  </si>
+  <si>
     <t xml:space="preserve">encuesta</t>
   </si>
   <si>
-    <t xml:space="preserve">percentil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor</t>
-  </si>
-  <si>
     <t xml:space="preserve">ENIGHUR 2011-2012 ajustada a precios 2024-2025</t>
   </si>
   <si>
-    <t xml:space="preserve">p10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p90</t>
-  </si>
-  <si>
     <t xml:space="preserve">p95</t>
   </si>
   <si>
@@ -312,45 +443,27 @@
     <t xml:space="preserve">alimentacion</t>
   </si>
   <si>
-    <t xml:space="preserve">Alimentos y restaurantes</t>
-  </si>
-  <si>
     <t xml:space="preserve">otros</t>
   </si>
   <si>
-    <t xml:space="preserve">Otros</t>
-  </si>
-  <si>
     <t xml:space="preserve">transporte</t>
   </si>
   <si>
     <t xml:space="preserve">recreacion_educacion</t>
   </si>
   <si>
-    <t xml:space="preserve">Recreación y educación</t>
-  </si>
-  <si>
     <t xml:space="preserve">vestimenta</t>
   </si>
   <si>
-    <t xml:space="preserve">Vestimenta</t>
-  </si>
-  <si>
     <t xml:space="preserve">salud</t>
   </si>
   <si>
     <t xml:space="preserve">vivienda</t>
   </si>
   <si>
-    <t xml:space="preserve">Vivienda y servicios</t>
-  </si>
-  <si>
     <t xml:space="preserve">hogar</t>
   </si>
   <si>
-    <t xml:space="preserve">Muebles y hogar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Original ENIGHUR</t>
   </si>
   <si>
@@ -433,6 +546,18 @@
   </si>
   <si>
     <t xml:space="preserve">Expenditure shares are weighted totals divided by the sum of the 13 original ENIGHUR consumption components. For 2024-2025, urban and rural shares are also shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income_quintile_definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income quintiles are defined from the weighted distribution of household monetary income (ing_mon_cor) in ENIGHUR 2024-2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gasoline_definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasolina is defined as the sum of ENIGHUR items c7222001 (eco país), c7222003 (extra), and c7222005 (súper) from ENIGHUR2025_GASTOS_HMO.</t>
   </si>
   <si>
     <t xml:space="preserve">agricultural_income_definition</t>
@@ -457,16 +582,27 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="20">
     <numFmt numFmtId="166" formatCode="$#,##0"/>
     <numFmt numFmtId="167" formatCode="$#,##0"/>
     <numFmt numFmtId="168" formatCode="$#,##0"/>
     <numFmt numFmtId="169" formatCode="$#,##0"/>
     <numFmt numFmtId="170" formatCode="$#,##0"/>
-    <numFmt numFmtId="171" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="$#,##0"/>
     <numFmt numFmtId="172" formatCode="$#,##0"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="173" formatCode="$#,##0"/>
     <numFmt numFmtId="174" formatCode="$#,##0"/>
+    <numFmt numFmtId="175" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="$#,##0"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="$#,##0"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
+    <numFmt numFmtId="180" formatCode="$#,##0"/>
+    <numFmt numFmtId="181" formatCode="$#,##0"/>
+    <numFmt numFmtId="182" formatCode="0.0%"/>
+    <numFmt numFmtId="183" formatCode="$#,##0"/>
+    <numFmt numFmtId="184" formatCode="0.0%"/>
+    <numFmt numFmtId="185" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -518,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -530,6 +666,17 @@
     <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="174" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="183" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="184" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="185" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -539,8 +686,120 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:B9" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:B9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:C31" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C31"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="quintil_ingreso"/>
+    <tableColumn id="2" name="percentil"/>
+    <tableColumn id="3" name="valor"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table11" displayName="Table11" ref="A1:G7" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:G7"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="quintil_ingreso"/>
+    <tableColumn id="2" name="weighted_mean_all"/>
+    <tableColumn id="3" name="weighted_median_all"/>
+    <tableColumn id="4" name="weighted_share_with_spend"/>
+    <tableColumn id="5" name="share_of_gasto_monetario"/>
+    <tableColumn id="6" name="weighted_mean_spenders"/>
+    <tableColumn id="7" name="weighted_median_spenders"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table12" displayName="Table12" ref="A1:G4" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:G4"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="zona"/>
+    <tableColumn id="2" name="weighted_mean_all"/>
+    <tableColumn id="3" name="weighted_median_all"/>
+    <tableColumn id="4" name="weighted_share_with_spend"/>
+    <tableColumn id="5" name="share_of_gasto_monetario"/>
+    <tableColumn id="6" name="weighted_mean_spenders"/>
+    <tableColumn id="7" name="weighted_median_spenders"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table13" displayName="Table13" ref="A1:C26" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C26"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="provincia"/>
+    <tableColumn id="2" name="weighted_households"/>
+    <tableColumn id="3" name="share_q5_households"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Table14" displayName="Table14" ref="A1:C15" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C15"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="encuesta"/>
+    <tableColumn id="2" name="percentil"/>
+    <tableColumn id="3" name="valor"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Table15" displayName="Table15" ref="A1:H42" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H42"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="encuesta"/>
+    <tableColumn id="2" name="nivel"/>
+    <tableColumn id="3" name="codigo"/>
+    <tableColumn id="4" name="componente"/>
+    <tableColumn id="5" name="weighted_total"/>
+    <tableColumn id="6" name="share_total"/>
+    <tableColumn id="7" name="share_urbana"/>
+    <tableColumn id="8" name="share_rural"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Table16" displayName="Table16" ref="A1:E10" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:E10"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="zona"/>
+    <tableColumn id="2" name="componente_ingreso"/>
+    <tableColumn id="3" name="weighted_mean"/>
+    <tableColumn id="4" name="weighted_median"/>
+    <tableColumn id="5" name="share_of_monetary_income"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table17" displayName="Table17" ref="A1:D7" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D7"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="encuesta"/>
+    <tableColumn id="2" name="zona"/>
+    <tableColumn id="3" name="media_ahorro"/>
+    <tableColumn id="4" name="mediana_ahorro"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Table18" displayName="Table18" ref="A1:B11" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:B11"/>
   <tableColumns count="2">
     <tableColumn id="1" name="item"/>
     <tableColumn id="2" name="detail"/>
@@ -596,56 +855,53 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C15" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C15"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="encuesta"/>
-    <tableColumn id="2" name="percentil"/>
-    <tableColumn id="3" name="valor"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:D55" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D55"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="zona"/>
+    <tableColumn id="2" name="indicador"/>
+    <tableColumn id="3" name="estadistico"/>
+    <tableColumn id="4" name="valor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:H42" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H42"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="encuesta"/>
-    <tableColumn id="2" name="nivel"/>
-    <tableColumn id="3" name="codigo"/>
-    <tableColumn id="4" name="componente"/>
-    <tableColumn id="5" name="weighted_total"/>
-    <tableColumn id="6" name="share_total"/>
-    <tableColumn id="7" name="share_urbana"/>
-    <tableColumn id="8" name="share_rural"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:E9" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:E9"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="componente"/>
+    <tableColumn id="2" name="variable"/>
+    <tableColumn id="3" name="mediana_urbana"/>
+    <tableColumn id="4" name="mediana_rural"/>
+    <tableColumn id="5" name="brecha_urbana_menos_rural"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:E10" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:E10"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="zona"/>
-    <tableColumn id="2" name="componente_ingreso"/>
-    <tableColumn id="3" name="weighted_mean"/>
-    <tableColumn id="4" name="weighted_median"/>
-    <tableColumn id="5" name="share_of_monetary_income"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:D85" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D85"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="quintil_ingreso"/>
+    <tableColumn id="2" name="indicador"/>
+    <tableColumn id="3" name="estadistico"/>
+    <tableColumn id="4" name="valor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:D7" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:D7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:D49" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D49"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="encuesta"/>
-    <tableColumn id="2" name="zona"/>
-    <tableColumn id="3" name="media_ahorro"/>
-    <tableColumn id="4" name="mediana_ahorro"/>
+    <tableColumn id="1" name="quintil_ingreso"/>
+    <tableColumn id="2" name="componente"/>
+    <tableColumn id="3" name="variable"/>
+    <tableColumn id="4" name="mediana"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1204,6 +1460,2059 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="6.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="25.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <v>20.5040907237554</v>
+      </c>
+      <c r="C2" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>0.315975613695782</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>0.0299904217930327</v>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>64.891370836917</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>21.8797317453531</v>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>0.317884413849874</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>0.0287550598691125</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>68.829205812167</v>
+      </c>
+      <c r="G3" t="n">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>16.2996509845606</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>0.310141653312187</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>0.0364075029314839</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>52.5555042687332</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId12"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="14" t="n">
+        <v>319098.514994572</v>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>0.292402390388259</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>260458.266472272</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>0.238668048060863</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>78443.7499122839</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>0.0718810615140618</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>59483.4999575758</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>0.0545070464416012</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>44061.2366170834</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>0.0403750262219711</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>38738.700484142</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.0354977791804848</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>36676.7118874571</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0.0336082987652147</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>31216.2941910675</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0.0286047054800194</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>31090.2185980512</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>0.0284891775065714</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>29658.5066100916</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>0.0271772440817667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>26510.0125129196</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0.0242921563835301</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>23464.6957858779</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>0.0215016141257841</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>16090.5601901746</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>0.0147444066368445</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>13914.7833147185</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>0.0127506575924603</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>10709.7493355717</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>0.00981376019952176</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>9717.45902066946</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>0.00890448595848852</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>9382.74402020098</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>0.00859777357457957</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>8436.03237611373</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>0.00773026484379083</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>8361.8733425669</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>0.00766231003466756</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>7546.50308192391</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>0.00691515452606996</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>7504.45716284067</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>0.00687662621375168</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>7373.55647522563</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>0.0067566768183032</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>7206.38106811468</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>0.00660348748536568</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>6154.76196471977</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>0.00563984796602834</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26"/>
+      <c r="B26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId13"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="46.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="16" t="n">
+        <v>195.844460882132</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>366.28082112636</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>613.625628496172</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>1057.79375066664</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>1794.67498053403</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>2526.07462845765</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>4748.17406649986</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>360.733333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>1825.83333333333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>4464.71666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId14"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="77.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>769223517.800168</v>
+      </c>
+      <c r="F2" s="18" t="n">
+        <v>0.321370561249857</v>
+      </c>
+      <c r="G2" s="18"/>
+      <c r="H2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>372420208.422937</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>0.155591825564491</v>
+      </c>
+      <c r="G3" s="18"/>
+      <c r="H3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>349497442.094873</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>0.146015022320986</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>213666453.857939</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.0892667821610089</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>190265816.446649</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0.079490331227765</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>179090619.560908</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0.0748214941314695</v>
+      </c>
+      <c r="G7" s="18"/>
+      <c r="H7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>177342239.420511</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.0740910459665403</v>
+      </c>
+      <c r="G8" s="18"/>
+      <c r="H8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>142065518.08612</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.0593529373778827</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>584496340.676835</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.24419419415177</v>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>349497442.094873</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0.146015022320986</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>236381682.046799</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0.0987568789443849</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>190265816.446649</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>0.079490331227765</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>184727177.123334</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0.0771763670980868</v>
+      </c>
+      <c r="G14" s="18"/>
+      <c r="H14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>179090619.560908</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0.0748214941314695</v>
+      </c>
+      <c r="G15" s="18"/>
+      <c r="H15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>177342239.420511</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>0.0740910459665403</v>
+      </c>
+      <c r="G16" s="18"/>
+      <c r="H16"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>142065518.08612</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>0.0593529373778827</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>118734692.098901</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0.0496056526570807</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>109284975.694428</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>0.0456576965763274</v>
+      </c>
+      <c r="G19" s="18"/>
+      <c r="H19"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>104381478.163511</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>0.0436090855846815</v>
+      </c>
+      <c r="G20" s="18"/>
+      <c r="H20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>17303834.2772361</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>0.00722929396302536</v>
+      </c>
+      <c r="G21" s="18"/>
+      <c r="H21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>1107446877.71723</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>0.315856500584576</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>0.310121607108244</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.345690246259151</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>559620972.638251</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>0.159610294297464</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>0.158920876390543</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.163196746004628</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>452151762.557502</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>0.128958847894306</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>0.124744961510816</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.150880094589721</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>380466223.100377</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>0.108513313132298</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>0.117349124476505</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0625481440215766</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>301298717.291203</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>0.0859338360954959</v>
+      </c>
+      <c r="G26" s="18" t="n">
+        <v>0.0925322984584298</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0516076801186755</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>269460042.233627</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>0.0768530822559395</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>0.0738261038676918</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0925998618203919</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>220025948.33015</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>0.0627539139580374</v>
+      </c>
+      <c r="G28" s="18" t="n">
+        <v>0.0610116749659327</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0718172932883232</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>215700377.634319</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>0.0615202117818818</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>0.0614933532218374</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0616599338975331</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>778733636.696796</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>0.222103729148221</v>
+      </c>
+      <c r="G30" s="18" t="n">
+        <v>0.212048450124372</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.274412745579379</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>452151762.557502</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>0.128958847894306</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>0.124744961510816</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.150880094589721</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>380466223.100377</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>0.108513313132298</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>0.117349124476505</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0625481440215766</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>328713241.020433</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>0.0937527714363551</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>0.0980731569838719</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.071277500679772</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>292043801.792885</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>0.0832942284706767</v>
+      </c>
+      <c r="G34" s="18" t="n">
+        <v>0.081470503208385</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0927815111691348</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>269460042.233627</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>0.0768530822559395</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>0.0738261038676918</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0925998618203919</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>220025948.33015</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>0.0627539139580374</v>
+      </c>
+      <c r="G36" s="18" t="n">
+        <v>0.0610116749659327</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0718172932883232</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B37" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>215700377.634319</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>0.0615202117818818</v>
+      </c>
+      <c r="G37" s="18" t="n">
+        <v>0.0614933532218374</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.0616599338975331</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>199790468.310692</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>0.0569825238939197</v>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>0.0572633163397419</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0555218009614761</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>196832203.476784</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>0.0561387929691764</v>
+      </c>
+      <c r="G39" s="18" t="n">
+        <v>0.0615918752004246</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0277710701682197</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>104466513.814419</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>0.0297950431263195</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>0.0309404232580051</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0238366099504558</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>49853845.9134065</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>0.0142188863662244</v>
+      </c>
+      <c r="G41" s="18" t="n">
+        <v>0.0153174200747643</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.00850415506201033</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>17932856.6212674</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>0.00511465556664357</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>0.00486963676765169</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.00638927881200656</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId15"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="6.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="23.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="19" t="n">
+        <v>20.3218368091516</v>
+      </c>
+      <c r="D2" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="20" t="n">
+        <v>0.0228587331610324</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>868.696669421741</v>
+      </c>
+      <c r="D3" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>0.977141266838968</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>889.018506230893</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>620</v>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>6.23321133684953</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>0.00632485723937293</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>979.276990861408</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>694.733333333333</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>0.993675142760627</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>985.510202198257</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>63.3816001314061</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>0.106683963879597</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>530.724560030944</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>386.1</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>0.893316036120403</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>594.10616016235</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>430</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId16"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="37.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="21" t="n">
+        <v>205.489620870764</v>
+      </c>
+      <c r="D2" s="21" t="n">
+        <v>68.56</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="21" t="n">
+        <v>224.790194168331</v>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>78.14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>146.500323454139</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>49.88</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>720.716464583814</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>448.555071775226</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>865.455973258512</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>558.649824332172</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>409.79912290714</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>286.132683289779</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId17"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="250.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId18"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -2092,13 +4401,13 @@
         <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>930.119614398551</v>
+        <v>683.687974289142</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>736.94</v>
+        <v>517.69</v>
       </c>
     </row>
     <row r="3">
@@ -2106,7 +4415,7 @@
         <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>889.018506230893</v>
@@ -2117,24 +4426,24 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1022.85310280638</v>
+        <v>760.900232687584</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>814.896666666667</v>
+        <v>580.283333333333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
         <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>985.510202198257</v>
@@ -2145,24 +4454,24 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>646.693664099959</v>
+        <v>447.700327463691</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>531.87</v>
+        <v>356.696666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>594.10616016235</v>
@@ -2185,174 +4494,780 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="46.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="6.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="33.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
         <v>79</v>
       </c>
-      <c r="B2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>195.844460882132</v>
+      <c r="D2" s="5" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>366.28082112636</v>
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>310.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>613.625628496172</v>
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>411.666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>1057.79375066664</v>
+        <v>74</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>505</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>1794.67498053403</v>
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>620</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>2526.07462845765</v>
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>770</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>4748.17406649986</v>
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>965.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>200</v>
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1262</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
         <v>87</v>
       </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>360.733333333333</v>
+      <c r="D10" s="5" t="n">
+        <v>1825.83333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>620</v>
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>189.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1100</v>
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>279.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>1825.83333333333</v>
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>358.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>2500</v>
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>435.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>517.69</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>617.48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>748.163333333333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>946.94</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
         <v>87</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D19" s="5" t="n">
+        <v>1320.92666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>241.666666666667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>362.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>571.08</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>861.67</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1077.33666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>4464.71666666667</v>
+      <c r="D27" s="5" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>229.006666666667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>328.32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>414.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>493.96</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>580.283333333333</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>687.906666666667</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>830.313333333333</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1053.01333333333</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1459.09583333333</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>142.916666666667</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>214.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>287.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>358.88</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>76</v>
+      </c>
+      <c r="B42" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>651.67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>836.741666666667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" t="s">
+        <v>87</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>1195.31</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>128.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" t="s">
+        <v>80</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>193.71</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>246.33</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>301.42</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>356.696666666667</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" t="s">
+        <v>84</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>422.32</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>76</v>
+      </c>
+      <c r="B53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" t="s">
+        <v>85</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>502.65</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>76</v>
+      </c>
+      <c r="B54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>622.97</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>834.37</v>
       </c>
     </row>
   </sheetData>
@@ -2369,1026 +5284,164 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="77.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="12.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="24.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="25.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>769223517.800168</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>0.321370561249857</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2"/>
+        <v>90</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>191.98</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>123.41</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>68.57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>372420208.422937</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>0.155591825564491</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3"/>
+        <v>92</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>28.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" t="s">
         <v>94</v>
       </c>
-      <c r="B4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>349497442.094873</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>0.146015022320986</v>
-      </c>
-      <c r="G4" s="7"/>
-      <c r="H4"/>
+      <c r="C4" s="6" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>5.22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>213666453.857939</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0.0892667821610089</v>
-      </c>
-      <c r="G5" s="7"/>
-      <c r="H5"/>
+        <v>96</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>8.01</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>190265816.446649</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>0.079490331227765</v>
-      </c>
-      <c r="G6" s="7"/>
-      <c r="H6"/>
+        <v>97</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>9.55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>179090619.560908</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>0.0748214941314695</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7"/>
+        <v>98</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>4.66</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>177342239.420511</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>0.0740910459665403</v>
-      </c>
-      <c r="G8" s="7"/>
-      <c r="H8"/>
+        <v>100</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>142065518.08612</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>0.0593529373778827</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>584496340.676835</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0.24419419415177</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>349497442.094873</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>0.146015022320986</v>
-      </c>
-      <c r="G11" s="7"/>
-      <c r="H11"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>236381682.046799</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>0.0987568789443849</v>
-      </c>
-      <c r="G12" s="7"/>
-      <c r="H12"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>190265816.446649</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>0.079490331227765</v>
-      </c>
-      <c r="G13" s="7"/>
-      <c r="H13"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>184727177.123334</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>0.0771763670980868</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>179090619.560908</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0.0748214941314695</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>177342239.420511</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>0.0740910459665403</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>142065518.08612</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0.0593529373778827</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>118734692.098901</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>0.0496056526570807</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>109284975.694428</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>0.0456576965763274</v>
-      </c>
-      <c r="G19" s="7"/>
-      <c r="H19"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>104381478.163511</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>0.0436090855846815</v>
-      </c>
-      <c r="G20" s="7"/>
-      <c r="H20"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>17303834.2772361</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>0.00722929396302536</v>
-      </c>
-      <c r="G21" s="7"/>
-      <c r="H21"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>1107446877.71723</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0.315856500584576</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>0.310121607108244</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.345690246259151</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>559620972.638251</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>0.159610294297464</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>0.158920876390543</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.163196746004628</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>452151762.557502</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0.128958847894306</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>0.124744961510816</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.150880094589721</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>380466223.100377</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>0.108513313132298</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>0.117349124476505</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.0625481440215766</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="7" t="n">
-        <v>301298717.291203</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>0.0859338360954959</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>0.0925322984584298</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0516076801186755</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>87</v>
-      </c>
-      <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="7" t="n">
-        <v>269460042.233627</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>0.0768530822559395</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>0.0738261038676918</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.0925998618203919</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>220025948.33015</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>0.0627539139580374</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>0.0610116749659327</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.0718172932883232</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>215700377.634319</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>0.0615202117818818</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>0.0614933532218374</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.0616599338975331</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>778733636.696796</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>0.222103729148221</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>0.212048450124372</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.274412745579379</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>452151762.557502</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>0.128958847894306</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>0.124744961510816</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.150880094589721</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" t="s">
-        <v>110</v>
-      </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>380466223.100377</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>0.108513313132298</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0.117349124476505</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.0625481440215766</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" t="s">
-        <v>110</v>
-      </c>
-      <c r="C33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>328713241.020433</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>0.0937527714363551</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>0.0980731569838719</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.071277500679772</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>292043801.792885</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>0.0832942284706767</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>0.081470503208385</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0927815111691348</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>269460042.233627</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>0.0768530822559395</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>0.0738261038676918</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.0925998618203919</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>87</v>
-      </c>
-      <c r="B36" t="s">
-        <v>110</v>
-      </c>
-      <c r="C36" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>220025948.33015</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>0.0627539139580374</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>0.0610116749659327</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.0718172932883232</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>215700377.634319</v>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>0.0615202117818818</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>0.0614933532218374</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.0616599338975331</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>199790468.310692</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>0.0569825238939197</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>0.0572633163397419</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.0555218009614761</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="7" t="n">
-        <v>196832203.476784</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>0.0561387929691764</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0.0615918752004246</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.0277710701682197</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>104466513.814419</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>0.0297950431263195</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>0.0309404232580051</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.0238366099504558</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>87</v>
-      </c>
-      <c r="B41" t="s">
-        <v>110</v>
-      </c>
-      <c r="C41" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" s="7" t="n">
-        <v>49853845.9134065</v>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>0.0142188863662244</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>0.0153174200747643</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.00850415506201033</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>87</v>
-      </c>
-      <c r="B42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>17932856.6212674</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>0.00511465556664357</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0.00486963676765169</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.00638927881200656</v>
+      <c r="C9" s="6" t="n">
+        <v>81.64</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>29.65</v>
       </c>
     </row>
   </sheetData>
@@ -3405,181 +5458,1200 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="6.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="23.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="15.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="33.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="8" t="n">
-        <v>20.3218368091516</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>0.0228587331610324</v>
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>310.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>868.696669421741</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>600</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0.977141266838968</v>
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>360.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>889.018506230893</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>620</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>1</v>
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>6.23321133684953</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.00632485723937293</v>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>620</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>979.276990861408</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>694.733333333333</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0.993675142760627</v>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>770</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>985.510202198257</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>700</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>1</v>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1099.99666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>63.3816001314061</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0.106683963879597</v>
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>530.724560030944</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>386.1</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.893316036120403</v>
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>279.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>594.10616016235</v>
-      </c>
-      <c r="D10" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>318.903333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>435.27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>517.69</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>617.48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>832.29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>946.94</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>116.666666666667</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>130.88</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>178.23</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>225.86</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>258.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>129.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>172.706666666667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>199.88</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>221.77</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>259.79</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>275.973333333333</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>360.503333333333</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>395.583333333333</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>411.84</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="7" t="n">
         <v>430</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>1</v>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>301.896666666667</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>317.97</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>356.99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>378.553333333333</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>403.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>444.46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>107</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>463.91</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>108</v>
+      </c>
+      <c r="B44" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>549.67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>559.996666666667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>598.333333333333</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>643.844166666667</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>689.166666666667</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>701.916666666667</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>430.713333333333</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>451.1025</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>507.14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" t="s">
+        <v>83</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>541.996666666667</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>574.39</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" t="s">
+        <v>105</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>635.186666666667</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
+        <v>86</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>859.646666666667</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>920.17</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>109</v>
+      </c>
+      <c r="B61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>965.583333333333</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>1012.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>109</v>
+      </c>
+      <c r="B63" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" t="s">
+        <v>86</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>569.683333333333</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>109</v>
+      </c>
+      <c r="B66" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>609.633333333333</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>109</v>
+      </c>
+      <c r="B67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>706.41</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>109</v>
+      </c>
+      <c r="B68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" t="s">
+        <v>83</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>761.276666666667</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>109</v>
+      </c>
+      <c r="B69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" t="s">
+        <v>84</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>815.06</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>109</v>
+      </c>
+      <c r="B70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" t="s">
+        <v>105</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>915.65</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>109</v>
+      </c>
+      <c r="B71" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>961.783333333333</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" t="s">
+        <v>74</v>
+      </c>
+      <c r="C72" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>1432.03</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>110</v>
+      </c>
+      <c r="B73" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" t="s">
+        <v>104</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>1480.57</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>110</v>
+      </c>
+      <c r="B74" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74" t="s">
+        <v>82</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>1677.83333333333</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75" t="s">
+        <v>83</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>1825.83333333333</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" t="s">
+        <v>74</v>
+      </c>
+      <c r="C76" t="s">
+        <v>84</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>2029.45333333333</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" t="s">
+        <v>105</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78" t="s">
+        <v>74</v>
+      </c>
+      <c r="C78" t="s">
+        <v>86</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>110</v>
+      </c>
+      <c r="B79" t="s">
+        <v>73</v>
+      </c>
+      <c r="C79" t="s">
+        <v>80</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>891.096666666667</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" t="s">
+        <v>104</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>972.416666666667</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>110</v>
+      </c>
+      <c r="B81" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" t="s">
+        <v>82</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>1151.95</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>110</v>
+      </c>
+      <c r="B82" t="s">
+        <v>73</v>
+      </c>
+      <c r="C82" t="s">
+        <v>83</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>1276.72333333333</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>110</v>
+      </c>
+      <c r="B83" t="s">
+        <v>73</v>
+      </c>
+      <c r="C83" t="s">
+        <v>84</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>1420.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>110</v>
+      </c>
+      <c r="B84" t="s">
+        <v>73</v>
+      </c>
+      <c r="C84" t="s">
+        <v>105</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>1772.88</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>110</v>
+      </c>
+      <c r="B85" t="s">
+        <v>73</v>
+      </c>
+      <c r="C85" t="s">
+        <v>86</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>1949.38333333333</v>
       </c>
     </row>
   </sheetData>
@@ -3596,108 +6668,696 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="37.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="6.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="24.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="10" t="n">
-        <v>205.489620870764</v>
-      </c>
-      <c r="D2" s="10" t="n">
-        <v>68.56</v>
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>172.96</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="10" t="n">
-        <v>224.790194168331</v>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>78.14</v>
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>71.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>146.500323454139</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>49.88</v>
+        <v>89</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>147.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>720.716464583814</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>448.555071775226</v>
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>189.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>865.455973258512</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>558.649824332172</v>
+        <v>89</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>226.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>409.79912290714</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>286.132683289779</v>
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>308.89</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>19.61</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>14.98</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>20.24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>26.41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>44.89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>25.34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>6.83</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>17.82</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>26.41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>39.49</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>67.15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>35.82</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>21.03</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>37.33</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>128.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>19.93</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>53.67</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" t="s">
+        <v>100</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" t="s">
+        <v>100</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>64.35</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>73.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>52.95</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>76.48</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>106.29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>174.91</v>
       </c>
     </row>
   </sheetData>
@@ -3714,80 +7374,350 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="250.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>113</v>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>189.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>104</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>318.903333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>114</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>517.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>105</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>832.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>115</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1320.92666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>113</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>81.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>104</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>129.03</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>114</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>199.88</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>259.79</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>314.11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>260.34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>317.97</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>378.553333333333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>444.46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>514.91</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>367.13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>451.1025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>541.996666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>635.186666666667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>733.35</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>476.973333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>609.633333333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>761.276666666667</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>915.65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>1096.36666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>712.096666666667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>972.416666666667</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>1276.72333333333</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>1772.88</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2516.84</v>
       </c>
     </row>
   </sheetData>
@@ -3797,4 +7727,188 @@
     <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="25.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="10" t="n">
+        <v>20.5040907237554</v>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>0.315975613695782</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>0.0299904217930327</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>64.891370836917</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>2.82696796493539</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>0.0883138074082332</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>0.0139682746641293</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>32.0104867845596</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>7.50100213863748</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>0.201013590887406</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>0.0193751637802597</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>37.315895435344</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27.46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>13.1194451129729</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0.281950489388383</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0.0237856882950075</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>46.5310244413197</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39.84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>23.4999054881802</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>0.402453657947179</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0.0299984378327904</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>58.3915813016774</v>
+      </c>
+      <c r="G6" t="n">
+        <v>43.76</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>55.6801127853221</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.607751622254603</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.0371966913608318</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>91.616559703721</v>
+      </c>
+      <c r="G7" t="n">
+        <v>85.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId11"/>
+  </tableParts>
+</worksheet>
 </file>